--- a/assuntos/aaaCTB 02 - Copia - Copia.xlsx
+++ b/assuntos/aaaCTB 02 - Copia - Copia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\attil\OneDrive\Área de Trabalho\App\PRF - Patrol\V6\R03\assuntos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\attil\patrol-game\assuntos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C354263-7D0D-4C7D-A121-258835DC73DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604C3264-AB4E-413F-8F07-286172776191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{8D551A73-E9FB-4C45-BB85-F4B67F836FE7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D551A73-E9FB-4C45-BB85-F4B67F836FE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,125 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="44">
-  <si>
-    <t>2. (2025 - Adaptada) Com relação à Condução de Veículos por Motoristas Profissionais, julgue os itens: Serão observados 15 min para descanso a cada 4 horas na condução de veículo rodoviário de passageiros, sendo facultado o seu fracionamento e o do tempo de direção.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="44">
   <si>
     <t>ERRADO</t>
   </si>
   <si>
-    <t>O intervalo para descanso na condução de veículo rodoviário de passageiros é de 30 minutos a cada 4 horas, e não 15 minutos, conforme estabelece o Art. 67-C, § 1º-A do CTB.</t>
-  </si>
-  <si>
-    <t>3. O condutor é obrigado, dentro do período de 48 horas, a observar o mínimo de 11 horas de descanso, que podem ser fracionadas ou até usufruídas no veículo.</t>
-  </si>
-  <si>
-    <t>O período correto para o descanso mínimo de 11 horas é de 24 horas, não 48 horas, de acordo com o Art. 67-C, § 3º do CTB.</t>
-  </si>
-  <si>
-    <t>4. O condutor somente iniciará uma viagem após o cumprimento integral do intervalo de descanso de 13 horas.</t>
-  </si>
-  <si>
-    <t>O intervalo mínimo de descanso é de 11 horas, não 13 horas, conforme Art. 67-C, § 6º do CTB.</t>
-  </si>
-  <si>
-    <t>11. (CESPE – MPU – Técnico Segurança) Incluem-se, entre as competências desse órgão, o acompanhamento e a coordenação das atividades de administração, educação, engenharia, fiscalização e policiamento ostensivo de trânsito.</t>
-  </si>
-  <si>
-    <t>Essa é uma competência do CETRAN e CONTRANDIFE (Art. 14, VIII), e não do CONTRAN.</t>
-  </si>
-  <si>
-    <t>12. (CESPE – MPU – Técnico Segurança) Ao CONTRAN compete coordenar os órgãos do Sistema Nacional de Trânsito.</t>
-  </si>
-  <si>
-    <t>Correto. É competência do CONTRAN coordenar os órgãos do SNT, conforme Art. 12, II do CTB.</t>
-  </si>
-  <si>
-    <t>13. (CESPE – MPU – Técnico Segurança) Compete a esse conselho normatizar os procedimentos sobre a aprendizagem, a habilitação e a expedição de documentos de condutores de veículos.</t>
-  </si>
-  <si>
-    <t>Correto. O CONTRAN tem competência para normatizar esses procedimentos, de acordo com o Art. 12, X do CTB.</t>
-  </si>
-  <si>
-    <t>22. (CESPE – CBM/DF) Conforme o CTB, a Polícia Militar do Distrito Federal e o Corpo de Bombeiros Militares do Distrito Federal integram o SNT.</t>
-  </si>
-  <si>
-    <t>A Polícia Militar integra o SNT, mas o Corpo de Bombeiros Militares não está listado no Art. 7º do CTB como componente do sistema.</t>
-  </si>
-  <si>
-    <t>23. (CESPE – CBM/DF) O órgão executivo com circunscrição sobre as vias urbanas do DF é o CONTRANDIFE.</t>
-  </si>
-  <si>
-    <t>O CONTRANDIFE é um órgão normativo e consultivo. O órgão executivo no DF é o DETRAN.</t>
-  </si>
-  <si>
-    <t>24. (CESPE - CETURB/ES – Agente de Trânsito) Entre as atribuições dos órgãos executivos de trânsito dos estados, inclui-se a de organizar e manter o registro nacional de veículos automotores.</t>
-  </si>
-  <si>
-    <t>Competência de organizar e manter o RENAVAM é do órgão máximo executivo de trânsito da União (SENATRAN), conforme Art. 19, IX do CTB.</t>
-  </si>
-  <si>
-    <t>25. (CESPE - CETURB/ES – Motorista) O sistema de estacionamento rotativo pago nas vias deve ser mantido e operado por entidade de trânsito dos estados.</t>
-  </si>
-  <si>
-    <t>A competência é dos órgãos executivos de trânsito dos Municípios, por ser assunto de interesse local (Art. 24, X do CTB).</t>
-  </si>
-  <si>
-    <t>26. (CESPE - DETRAN/DF – Analista de Trânsito) Os municípios integram automaticamente o SNT.</t>
-  </si>
-  <si>
-    <t>A integração não é automática. Os Municípios precisam criar órgão executivo de trânsito ou celebrar convênio, nos termos do Art. 24, § 2º do CTB.</t>
-  </si>
-  <si>
-    <t>27. (CESPE - DETRAN/DF – Analista de Trânsito) Compete ao Conselho de Trânsito do DF (CONTRANDIFE) responder a consultas relativas à aplicação da legislação e dos procedimentos normativos de trânsito.</t>
-  </si>
-  <si>
-    <t>Correto. É competência do CONTRANDIFE responder a consultas, conforme Art. 14, III do CTB.</t>
-  </si>
-  <si>
-    <t>28. (CESPE - DETRAN/DF – Auxiliar de Trânsito) O patrulhamento ostensivo das rodovias federais é de competência exclusiva dos DETRAN´s.</t>
-  </si>
-  <si>
-    <t>O patrulhamento ostensivo das rodovias federais é competência da PRF, de acordo com o Art. 20, II do CTB.</t>
-  </si>
-  <si>
-    <t>32. (CESPE – MPU – Técnico em Transportes) Na construção de trechos urbanos de vias rurais bem como na de obras de arte, devem ser previstos passeios destinados à circulação dos pedestres.</t>
-  </si>
-  <si>
-    <t>Correto. O Art. 68, § 5º do CTB estabelece a obrigatoriedade de passeios para pedestres nessas situações.</t>
-  </si>
-  <si>
-    <t>33. (CESPE – MPU – Técnico em Transportes) Considere que um ciclista esteja, desmontado, empurrando sua bicicleta em acostamento de via rural. Nessa situação, esse ciclista tem os mesmos direitos e deveres do pedestre.</t>
-  </si>
-  <si>
-    <t>Correto. Conforme Art. 68, § 1º do CTB, o ciclista desmontado empurrando a bicicleta equipara-se ao pedestre.</t>
-  </si>
-  <si>
-    <t>34. (CESPE – MPU – Técnico em Transportes) Em áreas urbanas, caso não haja passeios ou não seja possível a utilização destes, a circulação de veículos na pista de rolamento deve ser feita com prioridade sobre os pedestres, que devem andar pelos bordos da pista, em fila única.</t>
-  </si>
-  <si>
-    <t>Incorreto. Nessa situação, os pedestres têm prioridade sobre os veículos, de acordo com o Art. 68, § 2º do CTB.</t>
-  </si>
-  <si>
-    <t>35. (2025 - Adaptada) Suponha que um cidadão solicite, por escrito, a um órgão do Sistema Nacional de Trânsito, a implantação de sinalização de trânsito em determinada via. Neste caso, o referido órgão tem o dever de analisar a solicitação e responder, por escrito, dentro de um prazo não superior a 30 dias.</t>
-  </si>
-  <si>
-    <t>A lei fala em "prazos mínimos", mas não estabelece um prazo máximo de 30 dias. A resposta deve ser dada dentro de prazos mínimos (Art. 73 do CTB).</t>
-  </si>
-  <si>
-    <t>36. (2025 - Adaptada) A educação para o trânsito será promovida na pré-escola e nas escolas de 1º e 2º graus, sendo facultada nas escolas de 3º grau.</t>
-  </si>
-  <si>
-    <t>A educação para o trânsito deve ser promovida também nas escolas de 3º grau, não sendo facultativa (Art. 76 do CTB).</t>
-  </si>
-  <si>
-    <t>38. (2025 - Adaptada) A veiculação de publicidade feita em desacordo com o estabelecido no Código de Trânsito constitui infração punível com advertência por escrito ou suspensão, nos veículos de divulgação da publicidade, de qualquer outra propaganda do produto, pelo prazo de até 120 (cento e vinte) dias.</t>
-  </si>
-  <si>
-    <t>O prazo máximo de suspensão é de 60 dias, não 120, conforme Art. 77-E, II do CTB.</t>
-  </si>
-  <si>
     <t>Enunciado</t>
   </si>
   <si>
@@ -168,16 +54,136 @@
   </si>
   <si>
     <t>A1</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>c4</t>
+  </si>
+  <si>
+    <t>c5</t>
+  </si>
+  <si>
+    <t>c6</t>
+  </si>
+  <si>
+    <t>c7</t>
+  </si>
+  <si>
+    <t>c8</t>
+  </si>
+  <si>
+    <t>c9</t>
+  </si>
+  <si>
+    <t>c10</t>
+  </si>
+  <si>
+    <t>c11</t>
+  </si>
+  <si>
+    <t>c12</t>
+  </si>
+  <si>
+    <t>c13</t>
+  </si>
+  <si>
+    <t>c14</t>
+  </si>
+  <si>
+    <t>c15</t>
+  </si>
+  <si>
+    <t>c16</t>
+  </si>
+  <si>
+    <t>c17</t>
+  </si>
+  <si>
+    <t>c18</t>
+  </si>
+  <si>
+    <t>c19</t>
+  </si>
+  <si>
+    <t>c20</t>
+  </si>
+  <si>
+    <t>c21</t>
+  </si>
+  <si>
+    <t>c22</t>
+  </si>
+  <si>
+    <t>c23</t>
+  </si>
+  <si>
+    <t>c24</t>
+  </si>
+  <si>
+    <t>c25</t>
+  </si>
+  <si>
+    <t>c26</t>
+  </si>
+  <si>
+    <t>c27</t>
+  </si>
+  <si>
+    <t>c28</t>
+  </si>
+  <si>
+    <t>c29</t>
+  </si>
+  <si>
+    <t>c30</t>
+  </si>
+  <si>
+    <t>c31</t>
+  </si>
+  <si>
+    <t>c32</t>
+  </si>
+  <si>
+    <t>c33</t>
+  </si>
+  <si>
+    <t>c34</t>
+  </si>
+  <si>
+    <t>c35</t>
+  </si>
+  <si>
+    <t>c36</t>
+  </si>
+  <si>
+    <t>c37</t>
+  </si>
+  <si>
+    <t>c38</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -203,8 +209,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,442 +556,443 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
+      <c r="A3" s="1">
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
         <v>23</v>
       </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
         <v>25</v>
       </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
         <v>27</v>
       </c>
-      <c r="B16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
         <v>29</v>
       </c>
-      <c r="B17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
         <v>31</v>
       </c>
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
         <v>33</v>
       </c>
-      <c r="B19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
         <v>35</v>
       </c>
-      <c r="B20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
         <v>37</v>
       </c>
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>28</v>
-      </c>
-    </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>29</v>
+      <c r="A36" s="1">
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>31</v>
+      <c r="A37" s="1">
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>33</v>
+      <c r="A38" s="1">
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>35</v>
+      <c r="A39" s="1">
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>37</v>
+      <c r="A40" s="1">
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>